--- a/output/Tables/2019/Monte Carlo/HIA_per_disease.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_disease.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/Monte Carlo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD732C7D-8AE8-8147-960B-0A822E90D3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B46CC8-AFBF-CD40-A8E2-2C9FA3256BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="24740" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -139,11 +139,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -450,6 +451,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -497,22 +508,22 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>58632.906999999999</v>
+        <v>58497.2</v>
       </c>
       <c r="C2">
-        <v>55694.478999999999</v>
+        <v>55611.885000000002</v>
       </c>
       <c r="D2">
-        <v>61564.321000000004</v>
+        <v>61384.542000000001</v>
       </c>
       <c r="E2">
-        <v>605272.76100000006</v>
+        <v>604822.32700000005</v>
       </c>
       <c r="F2">
-        <v>587246.40300000005</v>
+        <v>587075.75800000003</v>
       </c>
       <c r="G2">
-        <v>623246.39300000004</v>
+        <v>622634.78200000001</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -523,14 +534,14 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>80553675311.802002</v>
-      </c>
-      <c r="L2">
-        <v>78207277278.429001</v>
-      </c>
-      <c r="M2">
-        <v>82850788045.126999</v>
+      <c r="K2" s="2">
+        <v>80441434320.218002</v>
+      </c>
+      <c r="L2" s="2">
+        <v>78067788489.720993</v>
+      </c>
+      <c r="M2" s="2">
+        <v>82813266773.876999</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -538,40 +549,40 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>40171.949000000001</v>
+        <v>40106.44</v>
       </c>
       <c r="C3">
-        <v>38472.478000000003</v>
+        <v>38353.705000000002</v>
       </c>
       <c r="D3">
-        <v>41921.235999999997</v>
+        <v>41862.716999999997</v>
       </c>
       <c r="E3">
-        <v>35945.027000000002</v>
+        <v>35899.445</v>
       </c>
       <c r="F3">
-        <v>34532.760999999999</v>
+        <v>34491.048999999999</v>
       </c>
       <c r="G3">
-        <v>37445.101000000002</v>
+        <v>37312.930999999997</v>
       </c>
       <c r="H3">
-        <v>2241240722.1259999</v>
+        <v>2233914624.5190001</v>
       </c>
       <c r="I3">
-        <v>2141141467.8210001</v>
+        <v>2136808039.3529999</v>
       </c>
       <c r="J3">
-        <v>2337023066.671</v>
-      </c>
-      <c r="K3">
-        <v>4781621561.691</v>
-      </c>
-      <c r="L3">
-        <v>4588713333.2810001</v>
-      </c>
-      <c r="M3">
-        <v>4969853707.5500002</v>
+        <v>2331780605.7849998</v>
+      </c>
+      <c r="K3" s="2">
+        <v>4774616176.3570004</v>
+      </c>
+      <c r="L3" s="2">
+        <v>4586974270.165</v>
+      </c>
+      <c r="M3" s="2">
+        <v>4962644964.4659996</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -579,40 +590,40 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>31005.238000000001</v>
+        <v>31194.030999999999</v>
       </c>
       <c r="C4">
-        <v>29501.508000000002</v>
+        <v>29746.760999999999</v>
       </c>
       <c r="D4">
-        <v>32542.332999999999</v>
+        <v>32692.708999999999</v>
       </c>
       <c r="E4">
-        <v>46563.900999999998</v>
+        <v>46946.311999999998</v>
       </c>
       <c r="F4">
-        <v>43965.061999999998</v>
+        <v>44287.932999999997</v>
       </c>
       <c r="G4">
-        <v>49524.355000000003</v>
+        <v>49747.894999999997</v>
       </c>
       <c r="H4">
-        <v>458041358.58099997</v>
+        <v>461943372.15399998</v>
       </c>
       <c r="I4">
-        <v>435967951.48100001</v>
+        <v>440485278.134</v>
       </c>
       <c r="J4">
-        <v>481614994.13800001</v>
-      </c>
-      <c r="K4">
-        <v>6194908569.6370001</v>
-      </c>
-      <c r="L4">
-        <v>5826763400.8500004</v>
-      </c>
-      <c r="M4">
-        <v>6581130445.2189999</v>
+        <v>484280083.06999999</v>
+      </c>
+      <c r="K4" s="2">
+        <v>6244102964.8839998</v>
+      </c>
+      <c r="L4" s="2">
+        <v>5890418483.8129997</v>
+      </c>
+      <c r="M4" s="2">
+        <v>6613973513.4379997</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -620,40 +631,40 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>6397.7619999999997</v>
+        <v>6403.3339999999998</v>
       </c>
       <c r="C5">
-        <v>6068.8530000000001</v>
+        <v>6093.9179999999997</v>
       </c>
       <c r="D5">
-        <v>6716.21</v>
+        <v>6716.7290000000003</v>
       </c>
       <c r="E5">
-        <v>12503.094999999999</v>
+        <v>12513.439</v>
       </c>
       <c r="F5">
-        <v>11835.61</v>
+        <v>11889.584999999999</v>
       </c>
       <c r="G5">
-        <v>13110.308000000001</v>
+        <v>13153.535</v>
       </c>
       <c r="H5">
-        <v>481037079.28299999</v>
+        <v>481494713.59500003</v>
       </c>
       <c r="I5">
-        <v>456135259.88200003</v>
+        <v>458301929.389</v>
       </c>
       <c r="J5">
-        <v>503854885.26200002</v>
-      </c>
-      <c r="K5">
-        <v>1663249345.8559999</v>
-      </c>
-      <c r="L5">
-        <v>1576109452.9519999</v>
-      </c>
-      <c r="M5">
-        <v>1749553460.217</v>
+        <v>505306374.19099998</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1664175730.319</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1581055798.0280001</v>
+      </c>
+      <c r="M5" s="2">
+        <v>1749081997.398</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -661,40 +672,40 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>13951.291999999999</v>
+        <v>13935.788</v>
       </c>
       <c r="C6">
-        <v>13145.431</v>
+        <v>13092.040999999999</v>
       </c>
       <c r="D6">
-        <v>14840.278</v>
+        <v>14790.941999999999</v>
       </c>
       <c r="E6">
-        <v>23272.392</v>
+        <v>23241.547999999999</v>
       </c>
       <c r="F6">
-        <v>22070.066999999999</v>
+        <v>22085.728999999999</v>
       </c>
       <c r="G6">
-        <v>24392.947</v>
+        <v>24404.937000000002</v>
       </c>
       <c r="H6">
-        <v>234909153.62799999</v>
+        <v>234630295.94499999</v>
       </c>
       <c r="I6">
-        <v>220993002.14300001</v>
+        <v>220486879.15400001</v>
       </c>
       <c r="J6">
-        <v>250108993.02700001</v>
-      </c>
-      <c r="K6">
-        <v>3092098448.848</v>
-      </c>
-      <c r="L6">
-        <v>2940554280.921</v>
-      </c>
-      <c r="M6">
-        <v>3255454542.3559999</v>
+        <v>248946325.111</v>
+      </c>
+      <c r="K6" s="2">
+        <v>3090943462.7080002</v>
+      </c>
+      <c r="L6" s="2">
+        <v>2937555833.5229998</v>
+      </c>
+      <c r="M6" s="2">
+        <v>3246066122.3850002</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -702,22 +713,22 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>151998.609</v>
+        <v>151929.28099999999</v>
       </c>
       <c r="C7">
-        <v>146283.32399999999</v>
+        <v>146460.71799999999</v>
       </c>
       <c r="D7">
-        <v>157395.59899999999</v>
+        <v>157416.94699999999</v>
       </c>
       <c r="E7">
-        <v>445589.13199999998</v>
+        <v>17510.058000000001</v>
       </c>
       <c r="F7">
-        <v>422056.85600000003</v>
+        <v>16826.866000000002</v>
       </c>
       <c r="G7">
-        <v>468172.69199999998</v>
+        <v>18202.366999999998</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -728,14 +739,14 @@
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
-        <v>59240445516.171997</v>
-      </c>
-      <c r="L7">
-        <v>56320429001.697998</v>
-      </c>
-      <c r="M7">
-        <v>62256163447.333</v>
+      <c r="K7" s="2">
+        <v>2328954679.9920001</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2237922028.4629998</v>
+      </c>
+      <c r="M7" s="2">
+        <v>2421236275.5040002</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -743,40 +754,40 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>243524.85</v>
+        <v>243568.87400000001</v>
       </c>
       <c r="C8">
-        <v>233471.59400000001</v>
+        <v>233747.14300000001</v>
       </c>
       <c r="D8">
-        <v>253415.65599999999</v>
+        <v>253480.04399999999</v>
       </c>
       <c r="E8">
-        <v>563873.54700000002</v>
+        <v>136110.802</v>
       </c>
       <c r="F8">
-        <v>534460.35600000003</v>
+        <v>129581.162</v>
       </c>
       <c r="G8">
-        <v>592645.40299999993</v>
+        <v>142821.66500000001</v>
       </c>
       <c r="H8">
-        <v>3415228313.618</v>
+        <v>3411983006.2129998</v>
       </c>
       <c r="I8">
-        <v>3254237681.3270001</v>
+        <v>3256082126.0300002</v>
       </c>
       <c r="J8">
-        <v>3572601939.098</v>
-      </c>
-      <c r="K8">
-        <v>74972323442.203995</v>
-      </c>
-      <c r="L8">
-        <v>71252569469.701996</v>
-      </c>
-      <c r="M8">
-        <v>78812155602.675003</v>
+        <v>3570313388.1570001</v>
+      </c>
+      <c r="K8" s="2">
+        <v>18102793014.259998</v>
+      </c>
+      <c r="L8" s="2">
+        <v>17233926413.992001</v>
+      </c>
+      <c r="M8" s="2">
+        <v>18993002873.191002</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -784,40 +795,40 @@
         <v>20</v>
       </c>
       <c r="B9">
-        <v>302157.75699999998</v>
+        <v>302066.07400000002</v>
       </c>
       <c r="C9">
-        <v>289166.07299999997</v>
+        <v>289359.02799999999</v>
       </c>
       <c r="D9">
-        <v>314979.97700000001</v>
+        <v>314864.58600000001</v>
       </c>
       <c r="E9">
-        <v>1169146.308</v>
+        <v>740933.12899999996</v>
       </c>
       <c r="F9">
-        <v>1121706.7590000001</v>
+        <v>716656.92</v>
       </c>
       <c r="G9">
-        <v>1215891.7960000001</v>
+        <v>765456.44700000004</v>
       </c>
       <c r="H9">
-        <v>3415228313.618</v>
+        <v>3411983006.2129998</v>
       </c>
       <c r="I9">
-        <v>3254237681.3270001</v>
+        <v>3256082126.0300002</v>
       </c>
       <c r="J9">
-        <v>3572601939.098</v>
-      </c>
-      <c r="K9">
-        <v>155525998754.00601</v>
-      </c>
-      <c r="L9">
-        <v>149459846748.13101</v>
-      </c>
-      <c r="M9">
-        <v>161662943647.802</v>
+        <v>3570313388.1570001</v>
+      </c>
+      <c r="K9" s="2">
+        <v>98544227334.477997</v>
+      </c>
+      <c r="L9" s="2">
+        <v>95301714903.712982</v>
+      </c>
+      <c r="M9" s="2">
+        <v>101806269647.06799</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Monte Carlo/HIA_per_disease.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_disease.xlsx
@@ -1,108 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/Monte Carlo/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B46CC8-AFBF-CD40-A8E2-2C9FA3256BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="24740" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,33 +52,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -203,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -237,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -272,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -448,82 +350,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
       </c>
       <c r="B2">
-        <v>58497.2</v>
+        <v>58496.197</v>
       </c>
       <c r="C2">
-        <v>55611.885000000002</v>
+        <v>55612.989</v>
       </c>
       <c r="D2">
-        <v>61384.542000000001</v>
+        <v>61379.951</v>
       </c>
       <c r="E2">
-        <v>604822.32700000005</v>
+        <v>604884.6580000001</v>
       </c>
       <c r="F2">
-        <v>587075.75800000003</v>
+        <v>587117.323</v>
       </c>
       <c r="G2">
-        <v>622634.78200000001</v>
+        <v>622704.426</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -534,201 +454,211 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" s="2">
-        <v>80441434320.218002</v>
-      </c>
-      <c r="L2" s="2">
-        <v>78067788489.720993</v>
-      </c>
-      <c r="M2" s="2">
-        <v>82813266773.876999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="K2">
+        <v>80450864508.582</v>
+      </c>
+      <c r="L2">
+        <v>78074500200.901</v>
+      </c>
+      <c r="M2">
+        <v>82820066431.078</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
       </c>
       <c r="B3">
-        <v>40106.44</v>
+        <v>40147.745</v>
       </c>
       <c r="C3">
-        <v>38353.705000000002</v>
+        <v>38394.954</v>
       </c>
       <c r="D3">
-        <v>41862.716999999997</v>
+        <v>41907.275</v>
       </c>
       <c r="E3">
-        <v>35899.445</v>
+        <v>35940.072</v>
       </c>
       <c r="F3">
-        <v>34491.048999999999</v>
+        <v>34538.407</v>
       </c>
       <c r="G3">
-        <v>37312.930999999997</v>
+        <v>37361.195</v>
       </c>
       <c r="H3">
-        <v>2233914624.5190001</v>
+        <v>2236285834.095</v>
       </c>
       <c r="I3">
-        <v>2136808039.3529999</v>
+        <v>2139020016.589</v>
       </c>
       <c r="J3">
-        <v>2331780605.7849998</v>
-      </c>
-      <c r="K3" s="2">
-        <v>4774616176.3570004</v>
-      </c>
-      <c r="L3" s="2">
-        <v>4586974270.165</v>
-      </c>
-      <c r="M3" s="2">
-        <v>4962644964.4659996</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
+        <v>2334382070.52</v>
+      </c>
+      <c r="K3">
+        <v>4780649331.573</v>
+      </c>
+      <c r="L3">
+        <v>4593104654.497</v>
+      </c>
+      <c r="M3">
+        <v>4968855086.343</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
       </c>
       <c r="B4">
-        <v>31194.030999999999</v>
+        <v>31225.536</v>
       </c>
       <c r="C4">
-        <v>29746.760999999999</v>
+        <v>29770.931</v>
       </c>
       <c r="D4">
-        <v>32692.708999999999</v>
+        <v>32738.557</v>
       </c>
       <c r="E4">
-        <v>46946.311999999998</v>
+        <v>47085.236</v>
       </c>
       <c r="F4">
-        <v>44287.932999999997</v>
+        <v>44414.475</v>
       </c>
       <c r="G4">
-        <v>49747.894999999997</v>
+        <v>49916.631</v>
       </c>
       <c r="H4">
-        <v>461943372.15399998</v>
+        <v>462381324.171</v>
       </c>
       <c r="I4">
-        <v>440485278.134</v>
+        <v>440895317.356</v>
       </c>
       <c r="J4">
-        <v>484280083.06999999</v>
-      </c>
-      <c r="K4" s="2">
-        <v>6244102964.8839998</v>
-      </c>
-      <c r="L4" s="2">
-        <v>5890418483.8129997</v>
-      </c>
-      <c r="M4" s="2">
-        <v>6613973513.4379997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
+        <v>484837826.929</v>
+      </c>
+      <c r="K4">
+        <v>6262145851.126</v>
+      </c>
+      <c r="L4">
+        <v>5905459759.404</v>
+      </c>
+      <c r="M4">
+        <v>6636403523.839</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
       </c>
       <c r="B5">
-        <v>6403.3339999999998</v>
+        <v>6404.258</v>
       </c>
       <c r="C5">
-        <v>6093.9179999999997</v>
+        <v>6095.128</v>
       </c>
       <c r="D5">
-        <v>6716.7290000000003</v>
+        <v>6721.067</v>
       </c>
       <c r="E5">
-        <v>12513.439</v>
+        <v>12502.744</v>
       </c>
       <c r="F5">
-        <v>11889.584999999999</v>
+        <v>11875.522</v>
       </c>
       <c r="G5">
-        <v>13153.535</v>
+        <v>13142.02</v>
       </c>
       <c r="H5">
-        <v>481494713.59500003</v>
+        <v>481611509.226</v>
       </c>
       <c r="I5">
-        <v>458301929.389</v>
+        <v>458313512.261</v>
       </c>
       <c r="J5">
-        <v>505306374.19099998</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1664175730.319</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1581055798.0280001</v>
-      </c>
-      <c r="M5" s="2">
-        <v>1749081997.398</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
+        <v>505193417.324</v>
+      </c>
+      <c r="K5">
+        <v>1662860969.4</v>
+      </c>
+      <c r="L5">
+        <v>1579278195.148</v>
+      </c>
+      <c r="M5">
+        <v>1747851369.462</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
       </c>
       <c r="B6">
-        <v>13935.788</v>
+        <v>13936.479</v>
       </c>
       <c r="C6">
-        <v>13092.040999999999</v>
+        <v>13089.929</v>
       </c>
       <c r="D6">
-        <v>14790.941999999999</v>
+        <v>14788.56</v>
       </c>
       <c r="E6">
-        <v>23241.547999999999</v>
+        <v>23252.174</v>
       </c>
       <c r="F6">
-        <v>22085.728999999999</v>
+        <v>22102.18</v>
       </c>
       <c r="G6">
-        <v>24404.937000000002</v>
+        <v>24412.371</v>
       </c>
       <c r="H6">
-        <v>234630295.94499999</v>
+        <v>234603634.648</v>
       </c>
       <c r="I6">
-        <v>220486879.15400001</v>
+        <v>220507915.673</v>
       </c>
       <c r="J6">
-        <v>248946325.111</v>
-      </c>
-      <c r="K6" s="2">
-        <v>3090943462.7080002</v>
-      </c>
-      <c r="L6" s="2">
-        <v>2937555833.5229998</v>
-      </c>
-      <c r="M6" s="2">
-        <v>3246066122.3850002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
+        <v>248863397.114</v>
+      </c>
+      <c r="K6">
+        <v>3092645316.941</v>
+      </c>
+      <c r="L6">
+        <v>2938681519.855</v>
+      </c>
+      <c r="M6">
+        <v>3246848652.597</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
       </c>
       <c r="B7">
-        <v>151929.28099999999</v>
+        <v>126005.061</v>
       </c>
       <c r="C7">
-        <v>146460.71799999999</v>
+        <v>121290.152</v>
       </c>
       <c r="D7">
-        <v>157416.94699999999</v>
+        <v>130799.503</v>
       </c>
       <c r="E7">
-        <v>17510.058000000001</v>
+        <v>41027.609</v>
       </c>
       <c r="F7">
-        <v>16826.866000000002</v>
+        <v>38919.728</v>
       </c>
       <c r="G7">
-        <v>18202.366999999998</v>
+        <v>43216.125</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -739,96 +669,100 @@
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7" s="2">
-        <v>2328954679.9920001</v>
-      </c>
-      <c r="L7" s="2">
-        <v>2237922028.4629998</v>
-      </c>
-      <c r="M7" s="2">
-        <v>2421236275.5040002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
+      <c r="K7">
+        <v>5456849853.619</v>
+      </c>
+      <c r="L7">
+        <v>5174349651.046</v>
+      </c>
+      <c r="M7">
+        <v>5748665005.371</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Morbidity</t>
+        </is>
       </c>
       <c r="B8">
-        <v>243568.87400000001</v>
+        <v>217719.079</v>
       </c>
       <c r="C8">
-        <v>233747.14300000001</v>
+        <v>208641.094</v>
       </c>
       <c r="D8">
-        <v>253480.04399999999</v>
+        <v>226954.962</v>
       </c>
       <c r="E8">
-        <v>136110.802</v>
+        <v>159807.835</v>
       </c>
       <c r="F8">
-        <v>129581.162</v>
+        <v>151850.312</v>
       </c>
       <c r="G8">
-        <v>142821.66500000001</v>
+        <v>168048.342</v>
       </c>
       <c r="H8">
-        <v>3411983006.2129998</v>
+        <v>3414882302.139999</v>
       </c>
       <c r="I8">
-        <v>3256082126.0300002</v>
+        <v>3258736761.879</v>
       </c>
       <c r="J8">
-        <v>3570313388.1570001</v>
-      </c>
-      <c r="K8" s="2">
-        <v>18102793014.259998</v>
-      </c>
-      <c r="L8" s="2">
-        <v>17233926413.992001</v>
-      </c>
-      <c r="M8" s="2">
-        <v>18993002873.191002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>20</v>
+        <v>3573276711.887</v>
+      </c>
+      <c r="K8">
+        <v>21255151322.659</v>
+      </c>
+      <c r="L8">
+        <v>20190873779.95</v>
+      </c>
+      <c r="M8">
+        <v>22348623637.612</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="B9">
-        <v>302066.07400000002</v>
+        <v>276215.276</v>
       </c>
       <c r="C9">
-        <v>289359.02799999999</v>
+        <v>264254.083</v>
       </c>
       <c r="D9">
-        <v>314864.58600000001</v>
+        <v>288334.913</v>
       </c>
       <c r="E9">
-        <v>740933.12899999996</v>
+        <v>764692.493</v>
       </c>
       <c r="F9">
-        <v>716656.92</v>
+        <v>738967.635</v>
       </c>
       <c r="G9">
-        <v>765456.44700000004</v>
+        <v>790752.768</v>
       </c>
       <c r="H9">
-        <v>3411983006.2129998</v>
+        <v>3414882302.139999</v>
       </c>
       <c r="I9">
-        <v>3256082126.0300002</v>
+        <v>3258736761.879</v>
       </c>
       <c r="J9">
-        <v>3570313388.1570001</v>
-      </c>
-      <c r="K9" s="2">
-        <v>98544227334.477997</v>
-      </c>
-      <c r="L9" s="2">
-        <v>95301714903.712982</v>
-      </c>
-      <c r="M9" s="2">
-        <v>101806269647.06799</v>
+        <v>3573276711.887</v>
+      </c>
+      <c r="K9">
+        <v>101706015831.241</v>
+      </c>
+      <c r="L9">
+        <v>98265373980.851</v>
+      </c>
+      <c r="M9">
+        <v>105168690068.69</v>
       </c>
     </row>
   </sheetData>
